--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008511962878429835</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>43902351</v>
+        <v>4081090</v>
       </c>
       <c r="L2" t="n">
-        <v>23304133</v>
+        <v>1621188</v>
       </c>
       <c r="M2" t="n">
-        <v>5557807</v>
+        <v>352624</v>
       </c>
       <c r="N2" t="n">
-        <v>217212</v>
+        <v>7769</v>
       </c>
       <c r="O2" t="n">
-        <v>3259701</v>
+        <v>199369</v>
       </c>
       <c r="P2" t="n">
-        <v>1259712</v>
+        <v>59430</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999072551727295</v>
+        <v>0.9999349117279053</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8431854844093323</v>
+        <v>0.7249449491500854</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7220770120620728</v>
+        <v>0.5591406226158142</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6442180275917053</v>
+        <v>0.4250996708869934</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2238574326038361</v>
+        <v>0.05546670779585838</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6995170116424561</v>
+        <v>0.4690814614295959</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8065223097801208</v>
+        <v>0.6413009166717529</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039737086905555</v>
       </c>
       <c r="C3" t="n">
-        <v>3550</v>
+        <v>276</v>
       </c>
       <c r="D3" t="n">
-        <v>43902351</v>
+        <v>4081090</v>
       </c>
       <c r="E3" t="n">
-        <v>5962657</v>
+        <v>827652</v>
       </c>
       <c r="F3" t="n">
-        <v>180796</v>
+        <v>44284</v>
       </c>
       <c r="G3" t="n">
-        <v>14082</v>
+        <v>3129</v>
       </c>
       <c r="H3" t="n">
-        <v>11712</v>
+        <v>3506</v>
       </c>
       <c r="I3" t="n">
-        <v>592</v>
+        <v>175</v>
       </c>
       <c r="J3" t="n">
-        <v>100160365</v>
+        <v>10016211</v>
       </c>
       <c r="K3" t="n">
-        <v>105055360</v>
+        <v>9821061</v>
       </c>
       <c r="L3" t="n">
-        <v>121517064</v>
+        <v>11732228</v>
       </c>
       <c r="M3" t="n">
-        <v>150874040</v>
+        <v>14910859</v>
       </c>
       <c r="N3" t="n">
-        <v>161649334</v>
+        <v>16107495</v>
       </c>
       <c r="O3" t="n">
-        <v>156795340</v>
+        <v>15592040</v>
       </c>
       <c r="P3" t="n">
-        <v>161059193</v>
+        <v>16102554</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8767189383506775</v>
+        <v>0.8227818012237549</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7102900147438049</v>
+        <v>0.4884373247623444</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5942556262016296</v>
+        <v>0.3743926882743835</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2430849969387054</v>
+        <v>0.08650676906108856</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6391031742095947</v>
+        <v>0.3894617855548859</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6511442065238953</v>
+        <v>0.3066484332084656</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0321438545796774</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7549679</v>
+        <v>1393100</v>
       </c>
       <c r="E4" t="n">
-        <v>23304133</v>
+        <v>1621188</v>
       </c>
       <c r="F4" t="n">
-        <v>1675291</v>
+        <v>244464</v>
       </c>
       <c r="G4" t="n">
-        <v>96323</v>
+        <v>21470</v>
       </c>
       <c r="H4" t="n">
-        <v>169203</v>
+        <v>35920</v>
       </c>
       <c r="I4" t="n">
-        <v>14680</v>
+        <v>2990</v>
       </c>
       <c r="J4" t="n">
-        <v>5855</v>
+        <v>411</v>
       </c>
       <c r="K4" t="n">
-        <v>8164900</v>
+        <v>1548427</v>
       </c>
       <c r="L4" t="n">
-        <v>8969616</v>
+        <v>1278240</v>
       </c>
       <c r="M4" t="n">
-        <v>3069407</v>
+        <v>476885</v>
       </c>
       <c r="N4" t="n">
-        <v>753102</v>
+        <v>132297</v>
       </c>
       <c r="O4" t="n">
-        <v>1400230</v>
+        <v>225651</v>
       </c>
       <c r="P4" t="n">
-        <v>302194</v>
+        <v>33241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999536275863647</v>
+        <v>0.9999674558639526</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8596253395080566</v>
+        <v>0.7707710266113281</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7161349654197693</v>
+        <v>0.5214030146598816</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6182290315628052</v>
+        <v>0.398138165473938</v>
       </c>
       <c r="U4" t="n">
-        <v>0.233075350522995</v>
+        <v>0.06759354472160339</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6679468154907227</v>
+        <v>0.4255797266960144</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7205520868301392</v>
+        <v>0.414903849363327</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1640</v>
+        <v>126</v>
       </c>
       <c r="D5" t="n">
-        <v>434435</v>
+        <v>115078</v>
       </c>
       <c r="E5" t="n">
-        <v>2462246</v>
+        <v>343480</v>
       </c>
       <c r="F5" t="n">
-        <v>5557807</v>
+        <v>352624</v>
       </c>
       <c r="G5" t="n">
-        <v>245966</v>
+        <v>39151</v>
       </c>
       <c r="H5" t="n">
-        <v>590165</v>
+        <v>81851</v>
       </c>
       <c r="I5" t="n">
-        <v>60294</v>
+        <v>9546</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6173389</v>
+        <v>879022</v>
       </c>
       <c r="L5" t="n">
-        <v>9505187</v>
+        <v>1697944</v>
       </c>
       <c r="M5" t="n">
-        <v>3794746</v>
+        <v>589232</v>
       </c>
       <c r="N5" t="n">
-        <v>676352</v>
+        <v>82039</v>
       </c>
       <c r="O5" t="n">
-        <v>1840729</v>
+        <v>312540</v>
       </c>
       <c r="P5" t="n">
-        <v>674901</v>
+        <v>134375</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999641180038452</v>
+        <v>0.9999748468399048</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9121944904327393</v>
+        <v>0.8513466715812683</v>
       </c>
       <c r="S5" t="n">
-        <v>0.886863112449646</v>
+        <v>0.8177430033683777</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9579649567604065</v>
+        <v>0.9347125887870789</v>
       </c>
       <c r="U5" t="n">
-        <v>0.991246223449707</v>
+        <v>0.9868744015693665</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9801528453826904</v>
+        <v>0.9670419692993164</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9940164089202881</v>
+        <v>0.9897354245185852</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>143214</v>
+        <v>24045</v>
       </c>
       <c r="E6" t="n">
-        <v>198652</v>
+        <v>22869</v>
       </c>
       <c r="F6" t="n">
-        <v>226702</v>
+        <v>25026</v>
       </c>
       <c r="G6" t="n">
-        <v>217212</v>
+        <v>7769</v>
       </c>
       <c r="H6" t="n">
-        <v>98324</v>
+        <v>9059</v>
       </c>
       <c r="I6" t="n">
-        <v>9157</v>
+        <v>1031</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>35354</v>
+        <v>15000</v>
       </c>
       <c r="E7" t="n">
-        <v>317164</v>
+        <v>75619</v>
       </c>
       <c r="F7" t="n">
-        <v>916166</v>
+        <v>144842</v>
       </c>
       <c r="G7" t="n">
-        <v>354462</v>
+        <v>57580</v>
       </c>
       <c r="H7" t="n">
-        <v>3259701</v>
+        <v>199369</v>
       </c>
       <c r="I7" t="n">
-        <v>217471</v>
+        <v>19499</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2218</v>
+        <v>1204</v>
       </c>
       <c r="E8" t="n">
-        <v>28897</v>
+        <v>8620</v>
       </c>
       <c r="F8" t="n">
-        <v>70452</v>
+        <v>18269</v>
       </c>
       <c r="G8" t="n">
-        <v>42269</v>
+        <v>10967</v>
       </c>
       <c r="H8" t="n">
-        <v>530826</v>
+        <v>95315</v>
       </c>
       <c r="I8" t="n">
-        <v>1259712</v>
+        <v>59430</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
